--- a/downloads/testimonials.xlsx
+++ b/downloads/testimonials.xlsx
@@ -456,7 +456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Testimonials and success stories</t>
+          <t>Dr. Johnson's patient testimonials and athlete stories</t>
         </is>
       </c>
     </row>

--- a/downloads/testimonials.xlsx
+++ b/downloads/testimonials.xlsx
@@ -456,7 +456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Dr. Johnson's patient testimonials and athlete stories</t>
+          <t>Patient testimonials and athlete stories from Dr. Johnson's websites</t>
         </is>
       </c>
     </row>

--- a/downloads/testimonials.xlsx
+++ b/downloads/testimonials.xlsx
@@ -8,9 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Every patient testimonial (31)," sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Patient testimonials" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Athlete success stories" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Where these came from" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -487,7 +487,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Every patient testimonial (31),</t>
+          <t>Patient testimonials</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -517,7 +517,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Where these came from</t>
+          <t>Sources</t>
         </is>
       </c>
       <c r="B7" t="n">
